--- a/STRRINGS.xlsx
+++ b/STRRINGS.xlsx
@@ -2132,7 +2132,7 @@
         <v>28</v>
       </c>
       <c r="E23" s="5">
-        <v>16500</v>
+        <v>48000</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>46</v>
